--- a/docs/pin_list.xlsx
+++ b/docs/pin_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/ExtraDesign/OpenSUSI-TR1um-v2609_01/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b2da16fa1785921/MyDocuments/Community/ISHIKAI/shuttle/OpenSUSI-TR10/2026/ExtraDesign/OpenSUSI-TR1um-v2609_03/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="441" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6027EC9-074C-47A5-B07B-A8C56CBB7DDE}"/>
+  <xr:revisionPtr revIDLastSave="482" documentId="11_AD4D066CA252ABDACC1048686197E6B673EEDF5D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6D09501-55D7-4F15-9935-8A12447F9296}"/>
   <bookViews>
     <workbookView xWindow="38330" yWindow="0" windowWidth="19200" windowHeight="9980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
   <si>
     <t>Pin Number</t>
     <phoneticPr fontId="1"/>
@@ -58,61 +58,39 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NMOS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>PMOS</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>G</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>共通・D端子</t>
-    <rPh sb="0" eb="2">
-      <t>キョウツウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>タンシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=30u</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>共通・D端子</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=16u</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=8u</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=4u</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=2u</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L=1u</t>
+    <t>AM_Radio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DETOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VREF</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RFINN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RFINP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VSS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RFOUT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>none</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -540,7 +518,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -551,7 +529,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -559,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -570,10 +548,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -581,33 +559,27 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" ht="18.350000000000001" thickTop="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1">
@@ -625,11 +597,9 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="18.350000000000001" thickBot="1">
       <c r="A11" s="5">
@@ -645,30 +615,30 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18.350000000000001" thickBot="1">
@@ -676,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.350000000000001" thickTop="1">
@@ -690,7 +660,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.350000000000001" thickBot="1">
